--- a/example_data/Becker_demo_dataset.xlsx
+++ b/example_data/Becker_demo_dataset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10413"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlson/Documents/GitHub/pharos-standard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cjs242/Documents/wdds/example_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7278F5-F016-9D40-8603-E23B7D9D836D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D85B4C82-119A-DF4B-8103-BAA2206E652F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12780" yWindow="760" windowWidth="21780" windowHeight="19140" xr2:uid="{ED439ACA-A8BD-8949-AE42-9D697BC62B76}"/>
+    <workbookView xWindow="12780" yWindow="600" windowWidth="21780" windowHeight="19140" xr2:uid="{ED439ACA-A8BD-8949-AE42-9D697BC62B76}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -103,9 +103,6 @@
     <t>BZ19-114</t>
   </si>
   <si>
-    <t>Collection method</t>
-  </si>
-  <si>
     <t>Oral swab</t>
   </si>
   <si>
@@ -152,6 +149,9 @@
   </si>
   <si>
     <t>Host life stage</t>
+  </si>
+  <si>
+    <t>Sample Collection method</t>
   </si>
 </sst>
 </file>
@@ -588,7 +588,7 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>7</v>
@@ -600,7 +600,7 @@
         <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>10</v>
@@ -653,46 +653,46 @@
         <v>2019</v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
         <v>25</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
       </c>
       <c r="M2">
         <v>2.3E-2</v>
       </c>
       <c r="N2" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" t="s">
         <v>29</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>32</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>33</v>
       </c>
-      <c r="S2" t="s">
-        <v>34</v>
-      </c>
       <c r="T2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" t="s">
         <v>36</v>
-      </c>
-      <c r="U2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
@@ -718,40 +718,40 @@
         <v>2019</v>
       </c>
       <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
         <v>24</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>25</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
       </c>
       <c r="M3">
         <v>2.3E-2</v>
       </c>
       <c r="N3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O3" t="s">
         <v>29</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>30</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>32</v>
       </c>
-      <c r="R3" t="s">
-        <v>33</v>
-      </c>
       <c r="S3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
